--- a/modle.xlsx
+++ b/modle.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CE8976-9F75-4E76-8C62-4F3DC2218275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31925184-A028-4A68-B9B3-6674DF3CA2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="22905" windowHeight="12075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HealthReport" sheetId="1" r:id="rId1"/>
@@ -1694,7 +1694,7 @@
   </si>
   <si>
     <t>sm0ora11节点的/ghome和/soft使用率超80%
-建议最近一段时间持续关注</t>
+建议最近一段时间持续关注aaa</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -2126,7 +2126,7 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2278,10 +2278,10 @@
     <xf numFmtId="0" fontId="22" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="37" fontId="22" fillId="7" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="22" fillId="7" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="14" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="14" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2296,19 +2296,16 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="37" fontId="22" fillId="2" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="22" fillId="2" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="14" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="14" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="14" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2317,20 +2314,20 @@
     <xf numFmtId="0" fontId="22" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="37" fontId="22" fillId="7" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="22" fillId="7" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="14" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="14" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="14" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" justifyLastLine="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -6771,7 +6768,7 @@
       <c r="I26" s="37"/>
       <c r="J26" s="37"/>
       <c r="K26" s="39"/>
-      <c r="L26" s="68">
+      <c r="L26" s="66">
         <f>SUM(HealthReport!$F$27:$F$39)/130</f>
         <v>0.52307692307692311</v>
       </c>
@@ -6896,11 +6893,11 @@
         <v>PASS</v>
       </c>
       <c r="H31" s="49"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="60"/>
-      <c r="K31" s="61"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="60"/>
       <c r="L31" s="52" t="str">
-        <f t="shared" ref="L30:L39" si="0">HYPERLINK("#OS!A1","Detail")</f>
+        <f t="shared" ref="L31:L39" si="0">HYPERLINK("#OS!A1","Detail")</f>
         <v>Detail</v>
       </c>
     </row>
@@ -7095,23 +7092,23 @@
       <c r="B39" s="23">
         <v>13</v>
       </c>
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="63">
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="62">
         <v>0</v>
       </c>
-      <c r="G39" s="64" t="str" cm="1">
+      <c r="G39" s="63" t="str" cm="1">
         <f t="array" ref="G39">_xlfn.IFS(HealthReport!$F39&gt;=10,"PASS",HealthReport!$F39=8,"轻微",HealthReport!$F39=5,"普通",HealthReport!$F39=0,"重要")</f>
         <v>重要</v>
       </c>
-      <c r="H39" s="62"/>
-      <c r="I39" s="62"/>
-      <c r="J39" s="62"/>
-      <c r="K39" s="65"/>
-      <c r="L39" s="65" t="str">
+      <c r="H39" s="61"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="64"/>
+      <c r="L39" s="64" t="str">
         <f t="shared" si="0"/>
         <v>Detail</v>
       </c>
@@ -7324,7 +7321,7 @@
       <c r="B5" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="66" t="str">
+      <c r="C5" s="65" t="str">
         <f>HYPERLINK("#HealthReport!B30","Retrun")</f>
         <v>Retrun</v>
       </c>
@@ -8030,35 +8027,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac37c1753acd5e330d2062ccec26ea66">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b340c7101c92c5120abd06486f94548" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8358,27 +8326,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D4997A-F5D7-47B8-8021-08C076C5E1C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1BB4A4-C009-44B7-9F89-7FA7A7BF749B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98E7F3D6-785F-49FE-8501-BF769B99AE88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8399,6 +8376,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1BB4A4-C009-44B7-9F89-7FA7A7BF749B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D4997A-F5D7-47B8-8021-08C076C5E1C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>